--- a/data/primary_data/abundance_biomass.xlsx
+++ b/data/primary_data/abundance_biomass.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\PostGrad\BSc Hons\4ZOL509_Research\primary_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87DA558-A6CE-491D-876E-DEA22BFD9A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB08D786-8A49-4C12-A7B3-52FB143B8BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0117D550-B72C-4C2F-8246-AE8BBB831B63}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="267">
   <si>
     <t>prawn_id</t>
   </si>
@@ -338,13 +338,496 @@
   </si>
   <si>
     <t>B326072</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>2.19</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>1.91</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>4.12</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>1.57</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>2.18</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>3.44</t>
+  </si>
+  <si>
+    <t>3.17</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>36.6</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>2.53</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>2.55</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>3.94</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>1.55</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>0.16</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>2.66</t>
+  </si>
+  <si>
+    <t>1.46</t>
+  </si>
+  <si>
+    <t>A119091</t>
+  </si>
+  <si>
+    <t>A119092</t>
+  </si>
+  <si>
+    <t>B219091</t>
+  </si>
+  <si>
+    <t>B219092</t>
+  </si>
+  <si>
+    <t>B219093</t>
+  </si>
+  <si>
+    <t>2.69</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>september</t>
+  </si>
+  <si>
+    <t>C319091</t>
+  </si>
+  <si>
+    <t>C319092</t>
+  </si>
+  <si>
+    <t>C319093</t>
+  </si>
+  <si>
+    <t>A219091</t>
+  </si>
+  <si>
+    <t>A219092</t>
+  </si>
+  <si>
+    <t>A219093</t>
+  </si>
+  <si>
+    <t>A319091</t>
+  </si>
+  <si>
+    <t>A319092</t>
+  </si>
+  <si>
+    <t>A319093</t>
+  </si>
+  <si>
+    <t>A319094</t>
+  </si>
+  <si>
+    <t>A319095</t>
+  </si>
+  <si>
+    <t>A319096</t>
+  </si>
+  <si>
+    <t>A319097</t>
+  </si>
+  <si>
+    <t>A319098</t>
+  </si>
+  <si>
+    <t>A319099</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>0.255</t>
+  </si>
+  <si>
+    <t>1.82</t>
+  </si>
+  <si>
+    <t>2.17</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>B119091</t>
+  </si>
+  <si>
+    <t>B119092</t>
+  </si>
+  <si>
+    <t>B119093</t>
+  </si>
+  <si>
+    <t>B119094</t>
+  </si>
+  <si>
+    <t>B219094</t>
+  </si>
+  <si>
+    <t>B219095</t>
+  </si>
+  <si>
+    <t>B319091</t>
+  </si>
+  <si>
+    <t>B319092</t>
+  </si>
+  <si>
+    <t>B319093</t>
+  </si>
+  <si>
+    <t>B319094</t>
+  </si>
+  <si>
+    <t>B319095</t>
+  </si>
+  <si>
+    <t>B319096</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>1.81</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>C119091</t>
+  </si>
+  <si>
+    <t>C119092</t>
+  </si>
+  <si>
+    <t>C119093</t>
+  </si>
+  <si>
+    <t>C119094</t>
+  </si>
+  <si>
+    <t>C119095</t>
+  </si>
+  <si>
+    <t>C119096</t>
+  </si>
+  <si>
+    <t>C119097</t>
+  </si>
+  <si>
+    <t>C119098</t>
+  </si>
+  <si>
+    <t>C119099</t>
+  </si>
+  <si>
+    <t>C1190910</t>
+  </si>
+  <si>
+    <t>C1190911</t>
+  </si>
+  <si>
+    <t>C1190912</t>
+  </si>
+  <si>
+    <t>C219091</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>2.68</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>1.77</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>C127071</t>
+  </si>
+  <si>
+    <t>2.39</t>
+  </si>
+  <si>
+    <t>C227072</t>
+  </si>
+  <si>
+    <t>C227071</t>
+  </si>
+  <si>
+    <t>C227073</t>
+  </si>
+  <si>
+    <t>C327071</t>
+  </si>
+  <si>
+    <t>C327072</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,6 +958,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1178,7 +1667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C9B8677-EBE5-423E-AF0C-F7A8B1945023}">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1217,8 +1706,8 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
-        <v>0.06</v>
+      <c r="B2" t="s">
+        <v>108</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1249,11 +1738,11 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3">
-        <v>2.19</v>
-      </c>
-      <c r="C3">
-        <v>0.49</v>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1281,8 +1770,8 @@
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
-        <v>0.19</v>
+      <c r="B4" t="s">
+        <v>111</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1313,11 +1802,11 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
-        <v>1.01</v>
-      </c>
-      <c r="C5">
-        <v>0.13</v>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" t="s">
+        <v>113</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1345,8 +1834,8 @@
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
-        <v>0.25</v>
+      <c r="B6" t="s">
+        <v>114</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1377,8 +1866,8 @@
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>0.15</v>
+      <c r="B7" t="s">
+        <v>115</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1409,8 +1898,8 @@
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
-        <v>0.19</v>
+      <c r="B8" t="s">
+        <v>111</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1441,8 +1930,8 @@
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9">
-        <v>7.0000000000000007E-2</v>
+      <c r="B9" t="s">
+        <v>116</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1473,8 +1962,8 @@
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
-        <v>0.09</v>
+      <c r="B10" t="s">
+        <v>117</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1505,8 +1994,8 @@
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11">
-        <v>0.04</v>
+      <c r="B11" t="s">
+        <v>118</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1537,8 +2026,8 @@
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12">
-        <v>0.05</v>
+      <c r="B12" t="s">
+        <v>119</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1569,11 +2058,11 @@
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13">
-        <v>1.02</v>
-      </c>
-      <c r="C13">
-        <v>0.19</v>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
       </c>
       <c r="D13">
         <v>26</v>
@@ -1601,11 +2090,11 @@
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
-        <v>1.91</v>
-      </c>
-      <c r="C14">
-        <v>0.39</v>
+      <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1633,8 +2122,8 @@
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15">
-        <v>0.22</v>
+      <c r="B15" t="s">
+        <v>123</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1665,8 +2154,8 @@
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16">
-        <v>0.15</v>
+      <c r="B16" t="s">
+        <v>115</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1697,8 +2186,8 @@
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17">
-        <v>0.1</v>
+      <c r="B17" t="s">
+        <v>124</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1729,8 +2218,8 @@
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18">
-        <v>0.15</v>
+      <c r="B18" t="s">
+        <v>115</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1761,8 +2250,8 @@
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19">
-        <v>0.11</v>
+      <c r="B19" t="s">
+        <v>125</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1793,8 +2282,8 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20">
-        <v>0.08</v>
+      <c r="B20" t="s">
+        <v>126</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1825,8 +2314,8 @@
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21">
-        <v>7.0000000000000007E-2</v>
+      <c r="B21" t="s">
+        <v>116</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1857,11 +2346,11 @@
       <c r="A22" t="s">
         <v>31</v>
       </c>
-      <c r="B22">
-        <v>4.12</v>
-      </c>
-      <c r="C22">
-        <v>0.92</v>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1889,11 +2378,11 @@
       <c r="A23" t="s">
         <v>32</v>
       </c>
-      <c r="B23">
-        <v>1.57</v>
-      </c>
-      <c r="C23">
-        <v>0.38</v>
+      <c r="B23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" t="s">
+        <v>130</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1921,11 +2410,11 @@
       <c r="A24" t="s">
         <v>33</v>
       </c>
-      <c r="B24">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="C24">
-        <v>0.63</v>
+      <c r="B24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" t="s">
+        <v>132</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1953,11 +2442,11 @@
       <c r="A25" t="s">
         <v>34</v>
       </c>
-      <c r="B25">
-        <v>1.44</v>
-      </c>
-      <c r="C25">
-        <v>0.32</v>
+      <c r="B25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1985,11 +2474,11 @@
       <c r="A26" t="s">
         <v>35</v>
       </c>
-      <c r="B26">
-        <v>1.32</v>
-      </c>
-      <c r="C26">
-        <v>0.31</v>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2017,8 +2506,8 @@
       <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="B27">
-        <v>0.06</v>
+      <c r="B27" t="s">
+        <v>108</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2049,8 +2538,8 @@
       <c r="A28" t="s">
         <v>37</v>
       </c>
-      <c r="B28">
-        <v>0.23</v>
+      <c r="B28" t="s">
+        <v>137</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2081,8 +2570,8 @@
       <c r="A29" t="s">
         <v>38</v>
       </c>
-      <c r="B29">
-        <v>7.0000000000000007E-2</v>
+      <c r="B29" t="s">
+        <v>116</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2113,11 +2602,11 @@
       <c r="A30" t="s">
         <v>39</v>
       </c>
-      <c r="B30">
-        <v>1.75</v>
-      </c>
-      <c r="C30">
-        <v>0.55000000000000004</v>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2145,11 +2634,11 @@
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31">
-        <v>3.44</v>
-      </c>
-      <c r="C31">
-        <v>0.92</v>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2177,8 +2666,8 @@
       <c r="A32" t="s">
         <v>41</v>
       </c>
-      <c r="B32">
-        <v>0.13</v>
+      <c r="B32" t="s">
+        <v>113</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2209,11 +2698,11 @@
       <c r="A33" t="s">
         <v>42</v>
       </c>
-      <c r="B33">
-        <v>3.17</v>
-      </c>
-      <c r="C33">
-        <v>0.8</v>
+      <c r="B33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" t="s">
+        <v>142</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2241,11 +2730,11 @@
       <c r="A34" t="s">
         <v>43</v>
       </c>
-      <c r="B34">
-        <v>1.8</v>
-      </c>
-      <c r="C34">
-        <v>0.42</v>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" t="s">
+        <v>144</v>
       </c>
       <c r="D34">
         <v>123</v>
@@ -2273,11 +2762,11 @@
       <c r="A35" t="s">
         <v>44</v>
       </c>
-      <c r="B35">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C35">
-        <v>0.73</v>
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" t="s">
+        <v>146</v>
       </c>
       <c r="D35">
         <v>103</v>
@@ -2305,8 +2794,8 @@
       <c r="A36" t="s">
         <v>45</v>
       </c>
-      <c r="B36">
-        <v>0.18</v>
+      <c r="B36" t="s">
+        <v>147</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2337,8 +2826,8 @@
       <c r="A37" t="s">
         <v>46</v>
       </c>
-      <c r="B37">
-        <v>0.1</v>
+      <c r="B37" t="s">
+        <v>124</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2369,11 +2858,11 @@
       <c r="A38" t="s">
         <v>47</v>
       </c>
-      <c r="B38">
-        <v>0.6</v>
-      </c>
-      <c r="C38">
-        <v>0.11</v>
+      <c r="B38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" t="s">
+        <v>125</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2381,8 +2870,8 @@
       <c r="E38">
         <v>10</v>
       </c>
-      <c r="F38">
-        <v>36.6</v>
+      <c r="F38" t="s">
+        <v>149</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2401,11 +2890,11 @@
       <c r="A39" t="s">
         <v>48</v>
       </c>
-      <c r="B39">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="C39">
-        <v>0.04</v>
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" t="s">
+        <v>118</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2433,11 +2922,11 @@
       <c r="A40" t="s">
         <v>49</v>
       </c>
-      <c r="B40">
-        <v>0.17</v>
-      </c>
-      <c r="C40">
-        <v>0.03</v>
+      <c r="B40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" t="s">
+        <v>152</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2465,11 +2954,11 @@
       <c r="A41" t="s">
         <v>50</v>
       </c>
-      <c r="B41">
-        <v>0.15</v>
-      </c>
-      <c r="C41">
-        <v>0.03</v>
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2497,8 +2986,8 @@
       <c r="A42" t="s">
         <v>51</v>
       </c>
-      <c r="B42">
-        <v>0.09</v>
+      <c r="B42" t="s">
+        <v>117</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2529,11 +3018,11 @@
       <c r="A43" t="s">
         <v>52</v>
       </c>
-      <c r="B43">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="C43">
-        <v>0.73</v>
+      <c r="B43" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2561,11 +3050,11 @@
       <c r="A44" t="s">
         <v>53</v>
       </c>
-      <c r="B44">
-        <v>0.45</v>
-      </c>
-      <c r="C44">
-        <v>0.08</v>
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>126</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2593,11 +3082,11 @@
       <c r="A45" t="s">
         <v>54</v>
       </c>
-      <c r="B45">
-        <v>0.49</v>
-      </c>
-      <c r="C45">
-        <v>0.09</v>
+      <c r="B45" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" t="s">
+        <v>117</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2625,11 +3114,11 @@
       <c r="A46" t="s">
         <v>55</v>
       </c>
-      <c r="B46">
-        <v>0.31</v>
-      </c>
-      <c r="C46">
-        <v>0.03</v>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" t="s">
+        <v>152</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2657,8 +3146,8 @@
       <c r="A47" t="s">
         <v>56</v>
       </c>
-      <c r="B47">
-        <v>0.13</v>
+      <c r="B47" t="s">
+        <v>113</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2689,8 +3178,8 @@
       <c r="A48" t="s">
         <v>57</v>
       </c>
-      <c r="B48">
-        <v>0.04</v>
+      <c r="B48" t="s">
+        <v>118</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2721,11 +3210,11 @@
       <c r="A49" t="s">
         <v>58</v>
       </c>
-      <c r="B49">
-        <v>0.83</v>
-      </c>
-      <c r="C49">
-        <v>0.1</v>
+      <c r="B49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" t="s">
+        <v>124</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2753,11 +3242,11 @@
       <c r="A50" t="s">
         <v>59</v>
       </c>
-      <c r="B50">
-        <v>1.23</v>
-      </c>
-      <c r="C50">
-        <v>0.25</v>
+      <c r="B50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" t="s">
+        <v>114</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2785,8 +3274,8 @@
       <c r="A51" t="s">
         <v>60</v>
       </c>
-      <c r="B51">
-        <v>0.08</v>
+      <c r="B51" t="s">
+        <v>126</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2817,11 +3306,11 @@
       <c r="A52" t="s">
         <v>61</v>
       </c>
-      <c r="B52">
-        <v>1.03</v>
-      </c>
-      <c r="C52">
-        <v>0.21</v>
+      <c r="B52" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52" t="s">
+        <v>157</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2849,11 +3338,11 @@
       <c r="A53" t="s">
         <v>62</v>
       </c>
-      <c r="B53">
-        <v>4.2</v>
-      </c>
-      <c r="C53">
-        <v>1.17</v>
+      <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2881,11 +3370,11 @@
       <c r="A54" t="s">
         <v>64</v>
       </c>
-      <c r="B54">
-        <v>0.8</v>
-      </c>
-      <c r="C54">
-        <v>0.17</v>
+      <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>151</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2913,11 +3402,11 @@
       <c r="A55" t="s">
         <v>65</v>
       </c>
-      <c r="B55">
-        <v>0.37</v>
-      </c>
-      <c r="C55">
-        <v>0.05</v>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" t="s">
+        <v>119</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2945,8 +3434,8 @@
       <c r="A56" t="s">
         <v>66</v>
       </c>
-      <c r="B56">
-        <v>0.19</v>
+      <c r="B56" t="s">
+        <v>111</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2977,8 +3466,8 @@
       <c r="A57" t="s">
         <v>67</v>
       </c>
-      <c r="B57">
-        <v>0.15</v>
+      <c r="B57" t="s">
+        <v>115</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3009,8 +3498,8 @@
       <c r="A58" t="s">
         <v>68</v>
       </c>
-      <c r="B58">
-        <v>0.13</v>
+      <c r="B58" t="s">
+        <v>113</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -3041,8 +3530,8 @@
       <c r="A59" t="s">
         <v>69</v>
       </c>
-      <c r="B59">
-        <v>0.06</v>
+      <c r="B59" t="s">
+        <v>108</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -3073,11 +3562,11 @@
       <c r="A60" t="s">
         <v>70</v>
       </c>
-      <c r="B60">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="C60">
-        <v>0.45</v>
+      <c r="B60" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" t="s">
+        <v>107</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3105,8 +3594,8 @@
       <c r="A61" t="s">
         <v>71</v>
       </c>
-      <c r="B61">
-        <v>0.28999999999999998</v>
+      <c r="B61" t="s">
+        <v>161</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3137,8 +3626,8 @@
       <c r="A62" t="s">
         <v>72</v>
       </c>
-      <c r="B62">
-        <v>0.28999999999999998</v>
+      <c r="B62" t="s">
+        <v>161</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3169,11 +3658,11 @@
       <c r="A63" t="s">
         <v>73</v>
       </c>
-      <c r="B63">
-        <v>0.51</v>
-      </c>
-      <c r="C63">
-        <v>0.05</v>
+      <c r="B63" t="s">
+        <v>162</v>
+      </c>
+      <c r="C63" t="s">
+        <v>119</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3201,8 +3690,8 @@
       <c r="A64" t="s">
         <v>74</v>
       </c>
-      <c r="B64">
-        <v>0.1</v>
+      <c r="B64" t="s">
+        <v>124</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3233,11 +3722,11 @@
       <c r="A65" t="s">
         <v>79</v>
       </c>
-      <c r="B65">
-        <v>0.26</v>
-      </c>
-      <c r="C65">
-        <v>0.05</v>
+      <c r="B65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" t="s">
+        <v>119</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3265,11 +3754,11 @@
       <c r="A66" t="s">
         <v>93</v>
       </c>
-      <c r="B66">
-        <v>1.05</v>
-      </c>
-      <c r="C66">
-        <v>0.17</v>
+      <c r="B66" t="s">
+        <v>164</v>
+      </c>
+      <c r="C66" t="s">
+        <v>151</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3297,11 +3786,11 @@
       <c r="A67" t="s">
         <v>92</v>
       </c>
-      <c r="B67">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C67">
-        <v>0.54</v>
+      <c r="B67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C67" t="s">
+        <v>166</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3329,11 +3818,11 @@
       <c r="A68" t="s">
         <v>91</v>
       </c>
-      <c r="B68">
-        <v>3.94</v>
-      </c>
-      <c r="C68">
-        <v>1.17</v>
+      <c r="B68" t="s">
+        <v>167</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3361,11 +3850,11 @@
       <c r="A69" t="s">
         <v>90</v>
       </c>
-      <c r="B69">
-        <v>0.48</v>
-      </c>
-      <c r="C69">
-        <v>7.0000000000000007E-2</v>
+      <c r="B69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" t="s">
+        <v>116</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3393,8 +3882,8 @@
       <c r="A70" t="s">
         <v>89</v>
       </c>
-      <c r="B70">
-        <v>0.12</v>
+      <c r="B70" t="s">
+        <v>169</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3425,11 +3914,11 @@
       <c r="A71" t="s">
         <v>94</v>
       </c>
-      <c r="B71">
-        <v>1.55</v>
-      </c>
-      <c r="C71">
-        <v>0.32</v>
+      <c r="B71" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" t="s">
+        <v>134</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3457,11 +3946,11 @@
       <c r="A72" t="s">
         <v>88</v>
       </c>
-      <c r="B72">
-        <v>0.81</v>
-      </c>
-      <c r="C72">
-        <v>0.16</v>
+      <c r="B72" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" t="s">
+        <v>172</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3489,8 +3978,8 @@
       <c r="A73" t="s">
         <v>87</v>
       </c>
-      <c r="B73">
-        <v>7.0000000000000007E-2</v>
+      <c r="B73" t="s">
+        <v>116</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3521,11 +4010,11 @@
       <c r="A74" t="s">
         <v>86</v>
       </c>
-      <c r="B74">
-        <v>0.3</v>
-      </c>
-      <c r="C74">
-        <v>0.05</v>
+      <c r="B74" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" t="s">
+        <v>119</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3553,11 +4042,11 @@
       <c r="A75" t="s">
         <v>85</v>
       </c>
-      <c r="B75">
-        <v>0.3</v>
-      </c>
-      <c r="C75">
-        <v>0.03</v>
+      <c r="B75" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" t="s">
+        <v>152</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3585,8 +4074,8 @@
       <c r="A76" t="s">
         <v>84</v>
       </c>
-      <c r="B76">
-        <v>0.13</v>
+      <c r="B76" t="s">
+        <v>113</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3617,11 +4106,11 @@
       <c r="A77" t="s">
         <v>80</v>
       </c>
-      <c r="B77">
-        <v>1.3</v>
-      </c>
-      <c r="C77">
-        <v>0.25</v>
+      <c r="B77" t="s">
+        <v>174</v>
+      </c>
+      <c r="C77" t="s">
+        <v>114</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3649,11 +4138,11 @@
       <c r="A78" t="s">
         <v>81</v>
       </c>
-      <c r="B78">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="C78">
-        <v>0.08</v>
+      <c r="B78" t="s">
+        <v>175</v>
+      </c>
+      <c r="C78" t="s">
+        <v>126</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3678,11 +4167,11 @@
       <c r="A79" t="s">
         <v>82</v>
       </c>
-      <c r="B79">
-        <v>0.33</v>
-      </c>
-      <c r="C79">
-        <v>0.04</v>
+      <c r="B79" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" t="s">
+        <v>118</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3710,8 +4199,8 @@
       <c r="A80" t="s">
         <v>83</v>
       </c>
-      <c r="B80">
-        <v>0.13</v>
+      <c r="B80" t="s">
+        <v>113</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3742,11 +4231,11 @@
       <c r="A81" t="s">
         <v>95</v>
       </c>
-      <c r="B81">
-        <v>0.86</v>
-      </c>
-      <c r="C81">
-        <v>0.1</v>
+      <c r="B81" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" t="s">
+        <v>124</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3774,11 +4263,11 @@
       <c r="A82" t="s">
         <v>96</v>
       </c>
-      <c r="B82">
-        <v>0.53</v>
-      </c>
-      <c r="C82">
-        <v>0.11</v>
+      <c r="B82" t="s">
+        <v>178</v>
+      </c>
+      <c r="C82" t="s">
+        <v>125</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3806,11 +4295,11 @@
       <c r="A83" t="s">
         <v>97</v>
       </c>
-      <c r="B83">
-        <v>1.24</v>
-      </c>
-      <c r="C83">
-        <v>0.23</v>
+      <c r="B83" t="s">
+        <v>179</v>
+      </c>
+      <c r="C83" t="s">
+        <v>137</v>
       </c>
       <c r="D83">
         <v>120</v>
@@ -3838,11 +4327,11 @@
       <c r="A84" t="s">
         <v>98</v>
       </c>
-      <c r="B84">
-        <v>0.85</v>
-      </c>
-      <c r="C84">
-        <v>0.19</v>
+      <c r="B84" t="s">
+        <v>180</v>
+      </c>
+      <c r="C84" t="s">
+        <v>111</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3870,11 +4359,11 @@
       <c r="A85" t="s">
         <v>99</v>
       </c>
-      <c r="B85">
-        <v>0.92</v>
-      </c>
-      <c r="C85">
-        <v>0.21</v>
+      <c r="B85" t="s">
+        <v>128</v>
+      </c>
+      <c r="C85" t="s">
+        <v>157</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3902,11 +4391,11 @@
       <c r="A86" t="s">
         <v>100</v>
       </c>
-      <c r="B86">
-        <v>0.62</v>
-      </c>
-      <c r="C86">
-        <v>0.13</v>
+      <c r="B86" t="s">
+        <v>181</v>
+      </c>
+      <c r="C86" t="s">
+        <v>113</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3934,11 +4423,11 @@
       <c r="A87" t="s">
         <v>101</v>
       </c>
-      <c r="B87">
-        <v>0.19</v>
-      </c>
-      <c r="C87">
-        <v>0.03</v>
+      <c r="B87" t="s">
+        <v>111</v>
+      </c>
+      <c r="C87" t="s">
+        <v>152</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3966,11 +4455,11 @@
       <c r="A88" t="s">
         <v>102</v>
       </c>
-      <c r="B88">
-        <v>0.23</v>
-      </c>
-      <c r="C88">
-        <v>0.03</v>
+      <c r="B88" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" t="s">
+        <v>152</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3998,11 +4487,11 @@
       <c r="A89" t="s">
         <v>103</v>
       </c>
-      <c r="B89">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C89">
-        <v>0.1</v>
+      <c r="B89" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" t="s">
+        <v>124</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -4030,8 +4519,8 @@
       <c r="A90" t="s">
         <v>104</v>
       </c>
-      <c r="B90">
-        <v>0.52</v>
+      <c r="B90" t="s">
+        <v>182</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4062,17 +4551,17 @@
       <c r="A91" t="s">
         <v>105</v>
       </c>
-      <c r="B91">
-        <v>0.33</v>
-      </c>
-      <c r="C91">
-        <v>0.03</v>
+      <c r="B91" t="s">
+        <v>176</v>
+      </c>
+      <c r="C91" t="s">
+        <v>152</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F91">
         <v>30</v>
@@ -4090,7 +4579,1496 @@
         <v>78</v>
       </c>
     </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>260</v>
+      </c>
+      <c r="B92" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" t="s">
+        <v>215</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>24</v>
+      </c>
+      <c r="F92">
+        <v>62</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>63</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>263</v>
+      </c>
+      <c r="B93" t="s">
+        <v>172</v>
+      </c>
+      <c r="C93" t="s">
+        <v>192</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>7</v>
+      </c>
+      <c r="F93">
+        <v>20</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+      <c r="H93" t="s">
+        <v>63</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>262</v>
+      </c>
+      <c r="B94" t="s">
+        <v>108</v>
+      </c>
+      <c r="C94" t="s">
+        <v>217</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>4</v>
+      </c>
+      <c r="F94">
+        <v>15</v>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="H94" t="s">
+        <v>63</v>
+      </c>
+      <c r="I94">
+        <v>3</v>
+      </c>
+      <c r="J94" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>264</v>
+      </c>
+      <c r="B95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" t="s">
+        <v>217</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>5</v>
+      </c>
+      <c r="F95">
+        <v>15</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+      <c r="H95" t="s">
+        <v>63</v>
+      </c>
+      <c r="I95">
+        <v>3</v>
+      </c>
+      <c r="J95" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>265</v>
+      </c>
+      <c r="B96" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96" t="s">
+        <v>217</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>4</v>
+      </c>
+      <c r="F96">
+        <v>16</v>
+      </c>
+      <c r="G96">
+        <v>3</v>
+      </c>
+      <c r="H96" t="s">
+        <v>63</v>
+      </c>
+      <c r="I96">
+        <v>3</v>
+      </c>
+      <c r="J96" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>266</v>
+      </c>
+      <c r="B97" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" t="s">
+        <v>217</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>4</v>
+      </c>
+      <c r="F97">
+        <v>17</v>
+      </c>
+      <c r="G97">
+        <v>3</v>
+      </c>
+      <c r="H97" t="s">
+        <v>63</v>
+      </c>
+      <c r="I97">
+        <v>3</v>
+      </c>
+      <c r="J97" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>185</v>
+      </c>
+      <c r="B98" t="s">
+        <v>183</v>
+      </c>
+      <c r="C98" t="s">
+        <v>106</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>15</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
+        <v>10</v>
+      </c>
+      <c r="I98">
+        <v>4</v>
+      </c>
+      <c r="J98" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>186</v>
+      </c>
+      <c r="B99" t="s">
+        <v>184</v>
+      </c>
+      <c r="C99" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>13</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
+        <v>10</v>
+      </c>
+      <c r="I99">
+        <v>4</v>
+      </c>
+      <c r="J99" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" t="s">
+        <v>157</v>
+      </c>
+      <c r="C100" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>9</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100" t="s">
+        <v>10</v>
+      </c>
+      <c r="I100">
+        <v>4</v>
+      </c>
+      <c r="J100" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>199</v>
+      </c>
+      <c r="B101" t="s">
+        <v>190</v>
+      </c>
+      <c r="C101" t="s">
+        <v>193</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>11</v>
+      </c>
+      <c r="F101">
+        <v>60</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+      <c r="H101" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101">
+        <v>4</v>
+      </c>
+      <c r="J101" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>191</v>
+      </c>
+      <c r="C102" t="s">
+        <v>115</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>12</v>
+      </c>
+      <c r="F102">
+        <v>45</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+      <c r="H102" t="s">
+        <v>10</v>
+      </c>
+      <c r="I102">
+        <v>4</v>
+      </c>
+      <c r="J102" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>201</v>
+      </c>
+      <c r="B103" t="s">
+        <v>210</v>
+      </c>
+      <c r="C103" t="s">
+        <v>118</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>10</v>
+      </c>
+      <c r="H103" t="s">
+        <v>10</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
+      </c>
+      <c r="J103" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>202</v>
+      </c>
+      <c r="B104" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" t="s">
+        <v>217</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>9</v>
+      </c>
+      <c r="F104">
+        <v>30</v>
+      </c>
+      <c r="H104" t="s">
+        <v>10</v>
+      </c>
+      <c r="I104">
+        <v>4</v>
+      </c>
+      <c r="J104" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>203</v>
+      </c>
+      <c r="B105" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" t="s">
+        <v>192</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>8</v>
+      </c>
+      <c r="F105">
+        <v>32</v>
+      </c>
+      <c r="H105" t="s">
+        <v>10</v>
+      </c>
+      <c r="I105">
+        <v>4</v>
+      </c>
+      <c r="J105" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>204</v>
+      </c>
+      <c r="B106" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" t="s">
+        <v>217</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
+      </c>
+      <c r="F106">
+        <v>16</v>
+      </c>
+      <c r="H106" t="s">
+        <v>10</v>
+      </c>
+      <c r="I106">
+        <v>4</v>
+      </c>
+      <c r="J106" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>205</v>
+      </c>
+      <c r="B107" t="s">
+        <v>161</v>
+      </c>
+      <c r="C107" t="s">
+        <v>217</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>3</v>
+      </c>
+      <c r="F107">
+        <v>27</v>
+      </c>
+      <c r="H107" t="s">
+        <v>10</v>
+      </c>
+      <c r="I107">
+        <v>4</v>
+      </c>
+      <c r="J107" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>206</v>
+      </c>
+      <c r="B108" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" t="s">
+        <v>217</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>5</v>
+      </c>
+      <c r="F108">
+        <v>28</v>
+      </c>
+      <c r="H108" t="s">
+        <v>10</v>
+      </c>
+      <c r="I108">
+        <v>4</v>
+      </c>
+      <c r="J108" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>207</v>
+      </c>
+      <c r="B109" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" t="s">
+        <v>216</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>13</v>
+      </c>
+      <c r="F109">
+        <v>55</v>
+      </c>
+      <c r="H109" t="s">
+        <v>10</v>
+      </c>
+      <c r="I109">
+        <v>4</v>
+      </c>
+      <c r="J109" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>208</v>
+      </c>
+      <c r="B110" t="s">
+        <v>213</v>
+      </c>
+      <c r="C110" t="s">
+        <v>161</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>18</v>
+      </c>
+      <c r="F110">
+        <v>58</v>
+      </c>
+      <c r="H110" t="s">
+        <v>10</v>
+      </c>
+      <c r="I110">
+        <v>4</v>
+      </c>
+      <c r="J110" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>209</v>
+      </c>
+      <c r="B111" t="s">
+        <v>214</v>
+      </c>
+      <c r="C111" t="s">
+        <v>215</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>18</v>
+      </c>
+      <c r="F111">
+        <v>60</v>
+      </c>
+      <c r="H111" t="s">
+        <v>10</v>
+      </c>
+      <c r="I111">
+        <v>4</v>
+      </c>
+      <c r="J111" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>218</v>
+      </c>
+      <c r="B112" t="s">
+        <v>230</v>
+      </c>
+      <c r="C112" t="s">
+        <v>115</v>
+      </c>
+      <c r="D112">
+        <v>72</v>
+      </c>
+      <c r="E112">
+        <v>9</v>
+      </c>
+      <c r="F112">
+        <v>40</v>
+      </c>
+      <c r="H112" t="s">
+        <v>12</v>
+      </c>
+      <c r="I112">
+        <v>4</v>
+      </c>
+      <c r="J112" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>219</v>
+      </c>
+      <c r="B113" t="s">
+        <v>164</v>
+      </c>
+      <c r="C113" t="s">
+        <v>147</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>8</v>
+      </c>
+      <c r="F113">
+        <v>49</v>
+      </c>
+      <c r="H113" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113">
+        <v>4</v>
+      </c>
+      <c r="J113" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>220</v>
+      </c>
+      <c r="B114" t="s">
+        <v>231</v>
+      </c>
+      <c r="C114" t="s">
+        <v>125</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>7</v>
+      </c>
+      <c r="F114">
+        <v>37</v>
+      </c>
+      <c r="H114" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114">
+        <v>4</v>
+      </c>
+      <c r="J114" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>221</v>
+      </c>
+      <c r="B115" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" t="s">
+        <v>217</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>5</v>
+      </c>
+      <c r="F115">
+        <v>25</v>
+      </c>
+      <c r="H115" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115">
+        <v>4</v>
+      </c>
+      <c r="J115" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>187</v>
+      </c>
+      <c r="B116" t="s">
+        <v>232</v>
+      </c>
+      <c r="C116" t="s">
+        <v>235</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>12</v>
+      </c>
+      <c r="F116">
+        <v>55</v>
+      </c>
+      <c r="H116" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116">
+        <v>4</v>
+      </c>
+      <c r="J116" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>188</v>
+      </c>
+      <c r="B117" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" t="s">
+        <v>236</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>11</v>
+      </c>
+      <c r="F117">
+        <v>54</v>
+      </c>
+      <c r="H117" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117">
+        <v>4</v>
+      </c>
+      <c r="J117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>189</v>
+      </c>
+      <c r="B118" t="s">
+        <v>154</v>
+      </c>
+      <c r="C118" t="s">
+        <v>115</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>14</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118">
+        <v>4</v>
+      </c>
+      <c r="J118" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>222</v>
+      </c>
+      <c r="B119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" t="s">
+        <v>172</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>10</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119">
+        <v>4</v>
+      </c>
+      <c r="J119" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>223</v>
+      </c>
+      <c r="B120" t="s">
+        <v>150</v>
+      </c>
+      <c r="C120" t="s">
+        <v>217</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>8</v>
+      </c>
+      <c r="F120">
+        <v>28</v>
+      </c>
+      <c r="H120" t="s">
+        <v>12</v>
+      </c>
+      <c r="I120">
+        <v>4</v>
+      </c>
+      <c r="J120" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>224</v>
+      </c>
+      <c r="B121" t="s">
+        <v>233</v>
+      </c>
+      <c r="C121" t="s">
+        <v>122</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>17</v>
+      </c>
+      <c r="F121">
+        <v>61</v>
+      </c>
+      <c r="H121" t="s">
+        <v>12</v>
+      </c>
+      <c r="I121">
+        <v>4</v>
+      </c>
+      <c r="J121" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>225</v>
+      </c>
+      <c r="B122" t="s">
+        <v>234</v>
+      </c>
+      <c r="C122" t="s">
+        <v>111</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>10</v>
+      </c>
+      <c r="F122">
+        <v>49</v>
+      </c>
+      <c r="H122" t="s">
+        <v>12</v>
+      </c>
+      <c r="I122">
+        <v>4</v>
+      </c>
+      <c r="J122" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>226</v>
+      </c>
+      <c r="B123" t="s">
+        <v>119</v>
+      </c>
+      <c r="C123" t="s">
+        <v>217</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>4</v>
+      </c>
+      <c r="F123">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123">
+        <v>4</v>
+      </c>
+      <c r="J123" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>227</v>
+      </c>
+      <c r="B124" t="s">
+        <v>117</v>
+      </c>
+      <c r="C124" t="s">
+        <v>217</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>5</v>
+      </c>
+      <c r="F124">
+        <v>20</v>
+      </c>
+      <c r="H124" t="s">
+        <v>12</v>
+      </c>
+      <c r="I124">
+        <v>4</v>
+      </c>
+      <c r="J124" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>228</v>
+      </c>
+      <c r="B125" t="s">
+        <v>108</v>
+      </c>
+      <c r="C125" t="s">
+        <v>217</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>4</v>
+      </c>
+      <c r="F125">
+        <v>18</v>
+      </c>
+      <c r="H125" t="s">
+        <v>12</v>
+      </c>
+      <c r="I125">
+        <v>4</v>
+      </c>
+      <c r="J125" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>229</v>
+      </c>
+      <c r="B126" t="s">
+        <v>175</v>
+      </c>
+      <c r="C126" t="s">
+        <v>237</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>9</v>
+      </c>
+      <c r="F126">
+        <v>39</v>
+      </c>
+      <c r="H126" t="s">
+        <v>12</v>
+      </c>
+      <c r="I126">
+        <v>4</v>
+      </c>
+      <c r="J126" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>238</v>
+      </c>
+      <c r="B127" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" t="s">
+        <v>259</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>21</v>
+      </c>
+      <c r="F127">
+        <v>66</v>
+      </c>
+      <c r="H127" t="s">
+        <v>63</v>
+      </c>
+      <c r="I127">
+        <v>4</v>
+      </c>
+      <c r="J127" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>239</v>
+      </c>
+      <c r="B128" t="s">
+        <v>252</v>
+      </c>
+      <c r="C128" t="s">
+        <v>258</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>16</v>
+      </c>
+      <c r="H128" t="s">
+        <v>63</v>
+      </c>
+      <c r="I128">
+        <v>4</v>
+      </c>
+      <c r="J128" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>240</v>
+      </c>
+      <c r="B129" t="s">
+        <v>253</v>
+      </c>
+      <c r="C129" t="s">
+        <v>137</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>63</v>
+      </c>
+      <c r="I129">
+        <v>4</v>
+      </c>
+      <c r="J129" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>241</v>
+      </c>
+      <c r="B130" t="s">
+        <v>254</v>
+      </c>
+      <c r="C130" t="s">
+        <v>193</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>18</v>
+      </c>
+      <c r="F130">
+        <v>57</v>
+      </c>
+      <c r="H130" t="s">
+        <v>63</v>
+      </c>
+      <c r="I130">
+        <v>4</v>
+      </c>
+      <c r="J130" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>242</v>
+      </c>
+      <c r="B131" t="s">
+        <v>255</v>
+      </c>
+      <c r="C131" t="s">
+        <v>125</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>11</v>
+      </c>
+      <c r="F131">
+        <v>40</v>
+      </c>
+      <c r="H131" t="s">
+        <v>63</v>
+      </c>
+      <c r="I131">
+        <v>4</v>
+      </c>
+      <c r="J131" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>243</v>
+      </c>
+      <c r="B132" t="s">
+        <v>256</v>
+      </c>
+      <c r="C132" t="s">
+        <v>169</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>9</v>
+      </c>
+      <c r="F132">
+        <v>38</v>
+      </c>
+      <c r="H132" t="s">
+        <v>63</v>
+      </c>
+      <c r="I132">
+        <v>4</v>
+      </c>
+      <c r="J132" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>244</v>
+      </c>
+      <c r="B133" t="s">
+        <v>257</v>
+      </c>
+      <c r="C133" t="s">
+        <v>117</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>8</v>
+      </c>
+      <c r="F133">
+        <v>35</v>
+      </c>
+      <c r="H133" t="s">
+        <v>63</v>
+      </c>
+      <c r="I133">
+        <v>4</v>
+      </c>
+      <c r="J133" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>245</v>
+      </c>
+      <c r="B134" t="s">
+        <v>137</v>
+      </c>
+      <c r="C134" t="s">
+        <v>217</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>6</v>
+      </c>
+      <c r="F134">
+        <v>30</v>
+      </c>
+      <c r="H134" t="s">
+        <v>63</v>
+      </c>
+      <c r="I134">
+        <v>4</v>
+      </c>
+      <c r="J134" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>246</v>
+      </c>
+      <c r="B135" t="s">
+        <v>111</v>
+      </c>
+      <c r="C135" t="s">
+        <v>217</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>5</v>
+      </c>
+      <c r="F135">
+        <v>25</v>
+      </c>
+      <c r="H135" t="s">
+        <v>63</v>
+      </c>
+      <c r="I135">
+        <v>4</v>
+      </c>
+      <c r="J135" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>247</v>
+      </c>
+      <c r="B136" t="s">
+        <v>113</v>
+      </c>
+      <c r="C136" t="s">
+        <v>217</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>4</v>
+      </c>
+      <c r="F136">
+        <v>21</v>
+      </c>
+      <c r="H136" t="s">
+        <v>63</v>
+      </c>
+      <c r="I136">
+        <v>4</v>
+      </c>
+      <c r="J136" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>248</v>
+      </c>
+      <c r="B137" t="s">
+        <v>237</v>
+      </c>
+      <c r="C137" t="s">
+        <v>217</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>3</v>
+      </c>
+      <c r="F137">
+        <v>20</v>
+      </c>
+      <c r="H137" t="s">
+        <v>63</v>
+      </c>
+      <c r="I137">
+        <v>4</v>
+      </c>
+      <c r="J137" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>249</v>
+      </c>
+      <c r="B138" t="s">
+        <v>116</v>
+      </c>
+      <c r="C138" t="s">
+        <v>217</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>3</v>
+      </c>
+      <c r="F138">
+        <v>18</v>
+      </c>
+      <c r="H138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I138">
+        <v>4</v>
+      </c>
+      <c r="J138" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>250</v>
+      </c>
+      <c r="B139" t="s">
+        <v>136</v>
+      </c>
+      <c r="C139" t="s">
+        <v>152</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>10</v>
+      </c>
+      <c r="F139">
+        <v>30</v>
+      </c>
+      <c r="H139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I139">
+        <v>4</v>
+      </c>
+      <c r="J139" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>195</v>
+      </c>
+      <c r="B140" t="s">
+        <v>215</v>
+      </c>
+      <c r="C140" t="s">
+        <v>117</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>12</v>
+      </c>
+      <c r="F140">
+        <v>33</v>
+      </c>
+      <c r="H140" t="s">
+        <v>63</v>
+      </c>
+      <c r="I140">
+        <v>4</v>
+      </c>
+      <c r="J140" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>196</v>
+      </c>
+      <c r="B141" t="s">
+        <v>108</v>
+      </c>
+      <c r="C141" t="s">
+        <v>217</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>4</v>
+      </c>
+      <c r="F141">
+        <v>20</v>
+      </c>
+      <c r="H141" t="s">
+        <v>63</v>
+      </c>
+      <c r="I141">
+        <v>4</v>
+      </c>
+      <c r="J141" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>197</v>
+      </c>
+      <c r="B142" t="s">
+        <v>136</v>
+      </c>
+      <c r="C142" t="s">
+        <v>118</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+      <c r="F142">
+        <v>33</v>
+      </c>
+      <c r="H142" t="s">
+        <v>63</v>
+      </c>
+      <c r="I142">
+        <v>4</v>
+      </c>
+      <c r="J142" t="s">
+        <v>194</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/primary_data/abundance_biomass.xlsx
+++ b/data/primary_data/abundance_biomass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F47BD7-E898-445A-A606-00962D59582E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4A0107-FE3E-4F7C-805D-C4191601F4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0117D550-B72C-4C2F-8246-AE8BBB831B63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0117D550-B72C-4C2F-8246-AE8BBB831B63}"/>
   </bookViews>
   <sheets>
     <sheet name="abundance_biomass" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="438">
   <si>
     <t>prawn_id</t>
   </si>
@@ -1325,6 +1325,15 @@
   </si>
   <si>
     <t>year</t>
+  </si>
+  <si>
+    <t>tides</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>high</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C9B8677-EBE5-423E-AF0C-F7A8B1945023}">
-  <dimension ref="A1:K261"/>
+  <dimension ref="A1:L261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -2181,7 +2190,7 @@
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2215,8 +2224,11 @@
       <c r="K1" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2250,8 +2262,11 @@
       <c r="K2">
         <v>2025</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2285,8 +2300,11 @@
       <c r="K3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2320,8 +2338,11 @@
       <c r="K4">
         <v>2025</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2355,8 +2376,11 @@
       <c r="K5">
         <v>2025</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2390,8 +2414,11 @@
       <c r="K6">
         <v>2025</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2425,8 +2452,11 @@
       <c r="K7">
         <v>2025</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -2460,8 +2490,11 @@
       <c r="K8">
         <v>2025</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -2495,8 +2528,11 @@
       <c r="K9">
         <v>2025</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -2530,8 +2566,11 @@
       <c r="K10">
         <v>2025</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2565,8 +2604,11 @@
       <c r="K11">
         <v>2025</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2600,8 +2642,11 @@
       <c r="K12">
         <v>2025</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2635,8 +2680,11 @@
       <c r="K13">
         <v>2025</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2670,8 +2718,11 @@
       <c r="K14">
         <v>2025</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2705,8 +2756,11 @@
       <c r="K15">
         <v>2025</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2740,8 +2794,11 @@
       <c r="K16">
         <v>2025</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2775,8 +2832,11 @@
       <c r="K17">
         <v>2025</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2810,8 +2870,11 @@
       <c r="K18">
         <v>2025</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2845,8 +2908,11 @@
       <c r="K19">
         <v>2025</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2880,8 +2946,11 @@
       <c r="K20">
         <v>2025</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2915,8 +2984,11 @@
       <c r="K21">
         <v>2025</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2950,8 +3022,11 @@
       <c r="K22">
         <v>2025</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2985,8 +3060,11 @@
       <c r="K23">
         <v>2025</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -3020,8 +3098,11 @@
       <c r="K24">
         <v>2025</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -3055,8 +3136,11 @@
       <c r="K25">
         <v>2025</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -3090,8 +3174,11 @@
       <c r="K26">
         <v>2025</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -3125,8 +3212,11 @@
       <c r="K27">
         <v>2025</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -3160,8 +3250,11 @@
       <c r="K28">
         <v>2025</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -3195,8 +3288,11 @@
       <c r="K29">
         <v>2025</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -3230,8 +3326,11 @@
       <c r="K30">
         <v>2025</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -3265,8 +3364,11 @@
       <c r="K31">
         <v>2025</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -3300,8 +3402,11 @@
       <c r="K32">
         <v>2025</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -3335,8 +3440,11 @@
       <c r="K33">
         <v>2025</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -3370,8 +3478,11 @@
       <c r="K34">
         <v>2025</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -3405,8 +3516,11 @@
       <c r="K35">
         <v>2025</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -3440,8 +3554,11 @@
       <c r="K36">
         <v>2025</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -3475,8 +3592,11 @@
       <c r="K37">
         <v>2025</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -3510,8 +3630,11 @@
       <c r="K38">
         <v>2025</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -3545,8 +3668,11 @@
       <c r="K39">
         <v>2025</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -3580,8 +3706,11 @@
       <c r="K40">
         <v>2025</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L40" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -3615,8 +3744,11 @@
       <c r="K41">
         <v>2025</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L41" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -3650,8 +3782,11 @@
       <c r="K42">
         <v>2025</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -3685,8 +3820,11 @@
       <c r="K43">
         <v>2025</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -3720,8 +3858,11 @@
       <c r="K44">
         <v>2025</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -3755,8 +3896,11 @@
       <c r="K45">
         <v>2025</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L45" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -3790,8 +3934,11 @@
       <c r="K46">
         <v>2025</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L46" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -3825,8 +3972,11 @@
       <c r="K47">
         <v>2025</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L47" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3860,8 +4010,11 @@
       <c r="K48">
         <v>2025</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L48" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -3895,8 +4048,11 @@
       <c r="K49">
         <v>2025</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L49" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3930,8 +4086,11 @@
       <c r="K50">
         <v>2025</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L50" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -3965,8 +4124,11 @@
       <c r="K51">
         <v>2025</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L51" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -4000,8 +4162,11 @@
       <c r="K52">
         <v>2025</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L52" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -4035,8 +4200,11 @@
       <c r="K53">
         <v>2025</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L53" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>60</v>
       </c>
@@ -4070,8 +4238,11 @@
       <c r="K54">
         <v>2025</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L54" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -4105,8 +4276,11 @@
       <c r="K55">
         <v>2025</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L55" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -4140,8 +4314,11 @@
       <c r="K56">
         <v>2025</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L56" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -4175,8 +4352,11 @@
       <c r="K57">
         <v>2025</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L57" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -4210,8 +4390,11 @@
       <c r="K58">
         <v>2025</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L58" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -4245,8 +4428,11 @@
       <c r="K59">
         <v>2025</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L59" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -4280,8 +4466,11 @@
       <c r="K60">
         <v>2025</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L60" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -4315,8 +4504,11 @@
       <c r="K61">
         <v>2025</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L61" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -4350,8 +4542,11 @@
       <c r="K62">
         <v>2025</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L62" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -4385,8 +4580,11 @@
       <c r="K63">
         <v>2025</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L63" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>70</v>
       </c>
@@ -4420,8 +4618,11 @@
       <c r="K64">
         <v>2025</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L64" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -4455,8 +4656,11 @@
       <c r="K65">
         <v>2025</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L65" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>89</v>
       </c>
@@ -4490,8 +4694,11 @@
       <c r="K66">
         <v>2025</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L66" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>88</v>
       </c>
@@ -4525,8 +4732,11 @@
       <c r="K67">
         <v>2025</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L67" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -4560,8 +4770,11 @@
       <c r="K68">
         <v>2025</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L68" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -4595,8 +4808,11 @@
       <c r="K69">
         <v>2025</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L69" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -4630,8 +4846,11 @@
       <c r="K70">
         <v>2025</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L70" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>90</v>
       </c>
@@ -4665,8 +4884,11 @@
       <c r="K71">
         <v>2025</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L71" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -4700,8 +4922,11 @@
       <c r="K72">
         <v>2025</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L72" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -4735,8 +4960,11 @@
       <c r="K73">
         <v>2025</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L73" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -4770,8 +4998,11 @@
       <c r="K74">
         <v>2025</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L74" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>81</v>
       </c>
@@ -4805,8 +5036,11 @@
       <c r="K75">
         <v>2025</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L75" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -4840,8 +5074,11 @@
       <c r="K76">
         <v>2025</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L76" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -4875,8 +5112,11 @@
       <c r="K77">
         <v>2025</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L77" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -4907,8 +5147,11 @@
       <c r="K78">
         <v>2025</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L78" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -4942,8 +5185,11 @@
       <c r="K79">
         <v>2025</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L79" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -4977,8 +5223,11 @@
       <c r="K80">
         <v>2025</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L80" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -5012,8 +5261,11 @@
       <c r="K81">
         <v>2025</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L81" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -5047,8 +5299,11 @@
       <c r="K82">
         <v>2025</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L82" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -5082,8 +5337,11 @@
       <c r="K83">
         <v>2025</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L83" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -5117,8 +5375,11 @@
       <c r="K84">
         <v>2025</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L84" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -5152,8 +5413,11 @@
       <c r="K85">
         <v>2025</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L85" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -5187,8 +5451,11 @@
       <c r="K86">
         <v>2025</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L86" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -5222,8 +5489,11 @@
       <c r="K87">
         <v>2025</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L87" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>98</v>
       </c>
@@ -5257,8 +5527,11 @@
       <c r="K88">
         <v>2025</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L88" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -5292,8 +5565,11 @@
       <c r="K89">
         <v>2025</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L89" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -5327,8 +5603,11 @@
       <c r="K90">
         <v>2025</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L90" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -5362,8 +5641,11 @@
       <c r="K91">
         <v>2025</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L91" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>245</v>
       </c>
@@ -5397,8 +5679,11 @@
       <c r="K92">
         <v>2025</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L92" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>248</v>
       </c>
@@ -5432,8 +5717,11 @@
       <c r="K93">
         <v>2025</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L93" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>247</v>
       </c>
@@ -5467,8 +5755,11 @@
       <c r="K94">
         <v>2025</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L94" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>249</v>
       </c>
@@ -5502,8 +5793,11 @@
       <c r="K95">
         <v>2025</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L95" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>250</v>
       </c>
@@ -5537,8 +5831,11 @@
       <c r="K96">
         <v>2025</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L96" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>251</v>
       </c>
@@ -5572,8 +5869,11 @@
       <c r="K97">
         <v>2025</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L97" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>171</v>
       </c>
@@ -5604,8 +5904,11 @@
       <c r="K98">
         <v>2025</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L98" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>172</v>
       </c>
@@ -5636,8 +5939,11 @@
       <c r="K99">
         <v>2025</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L99" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>184</v>
       </c>
@@ -5668,8 +5974,11 @@
       <c r="K100">
         <v>2025</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L100" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>185</v>
       </c>
@@ -5703,8 +6012,11 @@
       <c r="K101">
         <v>2025</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L101" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>186</v>
       </c>
@@ -5738,8 +6050,11 @@
       <c r="K102">
         <v>2025</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L102" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>187</v>
       </c>
@@ -5770,8 +6085,11 @@
       <c r="K103">
         <v>2025</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L103" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>188</v>
       </c>
@@ -5805,8 +6123,11 @@
       <c r="K104">
         <v>2025</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L104" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>189</v>
       </c>
@@ -5840,8 +6161,11 @@
       <c r="K105">
         <v>2025</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L105" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>190</v>
       </c>
@@ -5875,8 +6199,11 @@
       <c r="K106">
         <v>2025</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L106" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>191</v>
       </c>
@@ -5910,8 +6237,11 @@
       <c r="K107">
         <v>2025</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L107" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>192</v>
       </c>
@@ -5945,8 +6275,11 @@
       <c r="K108">
         <v>2025</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L108" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>193</v>
       </c>
@@ -5980,8 +6313,11 @@
       <c r="K109">
         <v>2025</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L109" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>194</v>
       </c>
@@ -6015,8 +6351,11 @@
       <c r="K110">
         <v>2025</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L110" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>195</v>
       </c>
@@ -6050,8 +6389,11 @@
       <c r="K111">
         <v>2025</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L111" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>203</v>
       </c>
@@ -6085,8 +6427,11 @@
       <c r="K112">
         <v>2025</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L112" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>204</v>
       </c>
@@ -6120,8 +6465,11 @@
       <c r="K113">
         <v>2025</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L113" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>205</v>
       </c>
@@ -6155,8 +6503,11 @@
       <c r="K114">
         <v>2025</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L114" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>206</v>
       </c>
@@ -6190,8 +6541,11 @@
       <c r="K115">
         <v>2025</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L115" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>173</v>
       </c>
@@ -6225,8 +6579,11 @@
       <c r="K116">
         <v>2025</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L116" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>174</v>
       </c>
@@ -6260,8 +6617,11 @@
       <c r="K117">
         <v>2025</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L117" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>175</v>
       </c>
@@ -6292,8 +6652,11 @@
       <c r="K118">
         <v>2025</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L118" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>207</v>
       </c>
@@ -6324,8 +6687,11 @@
       <c r="K119">
         <v>2025</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L119" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>208</v>
       </c>
@@ -6359,8 +6725,11 @@
       <c r="K120">
         <v>2025</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L120" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
@@ -6394,8 +6763,11 @@
       <c r="K121">
         <v>2025</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L121" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>210</v>
       </c>
@@ -6429,8 +6801,11 @@
       <c r="K122">
         <v>2025</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L122" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>211</v>
       </c>
@@ -6464,8 +6839,11 @@
       <c r="K123">
         <v>2025</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L123" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>212</v>
       </c>
@@ -6499,8 +6877,11 @@
       <c r="K124">
         <v>2025</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L124" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>213</v>
       </c>
@@ -6534,8 +6915,11 @@
       <c r="K125">
         <v>2025</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L125" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>214</v>
       </c>
@@ -6569,8 +6953,11 @@
       <c r="K126">
         <v>2025</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L126" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>223</v>
       </c>
@@ -6604,8 +6991,11 @@
       <c r="K127">
         <v>2025</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L127" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>224</v>
       </c>
@@ -6636,8 +7026,11 @@
       <c r="K128">
         <v>2025</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L128" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>225</v>
       </c>
@@ -6668,8 +7061,11 @@
       <c r="K129">
         <v>2025</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L129" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>226</v>
       </c>
@@ -6703,8 +7099,11 @@
       <c r="K130">
         <v>2025</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L130" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>227</v>
       </c>
@@ -6738,8 +7137,11 @@
       <c r="K131">
         <v>2025</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L131" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>228</v>
       </c>
@@ -6773,8 +7175,11 @@
       <c r="K132">
         <v>2025</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L132" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -6808,8 +7213,11 @@
       <c r="K133">
         <v>2025</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L133" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -6843,8 +7251,11 @@
       <c r="K134">
         <v>2025</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L134" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>231</v>
       </c>
@@ -6878,8 +7289,11 @@
       <c r="K135">
         <v>2025</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L135" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>232</v>
       </c>
@@ -6913,8 +7327,11 @@
       <c r="K136">
         <v>2025</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L136" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>233</v>
       </c>
@@ -6948,8 +7365,11 @@
       <c r="K137">
         <v>2025</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L137" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>234</v>
       </c>
@@ -6983,8 +7403,11 @@
       <c r="K138">
         <v>2025</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L138" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>235</v>
       </c>
@@ -7018,8 +7441,11 @@
       <c r="K139">
         <v>2025</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L139" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>181</v>
       </c>
@@ -7053,8 +7479,11 @@
       <c r="K140">
         <v>2025</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L140" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>182</v>
       </c>
@@ -7088,8 +7517,11 @@
       <c r="K141">
         <v>2025</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L141" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>183</v>
       </c>
@@ -7123,8 +7555,11 @@
       <c r="K142">
         <v>2025</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L142" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>252</v>
       </c>
@@ -7158,8 +7593,11 @@
       <c r="K143">
         <v>2025</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L143" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>255</v>
       </c>
@@ -7193,8 +7631,11 @@
       <c r="K144">
         <v>2025</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L144" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>254</v>
       </c>
@@ -7228,8 +7669,11 @@
       <c r="K145">
         <v>2025</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L145" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>253</v>
       </c>
@@ -7263,8 +7707,11 @@
       <c r="K146">
         <v>2025</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L146" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>256</v>
       </c>
@@ -7298,8 +7745,11 @@
       <c r="K147">
         <v>2025</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L147" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>257</v>
       </c>
@@ -7333,8 +7783,11 @@
       <c r="K148">
         <v>2025</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L148" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>258</v>
       </c>
@@ -7368,8 +7821,11 @@
       <c r="K149">
         <v>2025</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L149" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>259</v>
       </c>
@@ -7403,8 +7859,11 @@
       <c r="K150">
         <v>2025</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L150" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>260</v>
       </c>
@@ -7438,8 +7897,11 @@
       <c r="K151">
         <v>2025</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L151" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>261</v>
       </c>
@@ -7473,8 +7935,11 @@
       <c r="K152">
         <v>2025</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L152" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>262</v>
       </c>
@@ -7508,8 +7973,11 @@
       <c r="K153">
         <v>2025</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L153" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>263</v>
       </c>
@@ -7543,8 +8011,11 @@
       <c r="K154">
         <v>2025</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L154" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>264</v>
       </c>
@@ -7578,8 +8049,11 @@
       <c r="K155">
         <v>2025</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L155" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>265</v>
       </c>
@@ -7613,8 +8087,11 @@
       <c r="K156">
         <v>2025</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L156" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>266</v>
       </c>
@@ -7648,8 +8125,11 @@
       <c r="K157">
         <v>2025</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L157" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>267</v>
       </c>
@@ -7683,8 +8163,11 @@
       <c r="K158">
         <v>2025</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L158" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>268</v>
       </c>
@@ -7718,8 +8201,11 @@
       <c r="K159">
         <v>2025</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L159" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>269</v>
       </c>
@@ -7753,8 +8239,11 @@
       <c r="K160">
         <v>2025</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L160" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>316</v>
       </c>
@@ -7788,8 +8277,11 @@
       <c r="K161">
         <v>2025</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L161" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>270</v>
       </c>
@@ -7823,8 +8315,11 @@
       <c r="K162">
         <v>2025</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L162" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>271</v>
       </c>
@@ -7858,8 +8353,11 @@
       <c r="K163">
         <v>2025</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L163" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>272</v>
       </c>
@@ -7893,8 +8391,11 @@
       <c r="K164">
         <v>2025</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L164" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>273</v>
       </c>
@@ -7928,8 +8429,11 @@
       <c r="K165">
         <v>2025</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L165" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>274</v>
       </c>
@@ -7963,8 +8467,11 @@
       <c r="K166">
         <v>2025</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L166" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>275</v>
       </c>
@@ -7998,8 +8505,11 @@
       <c r="K167">
         <v>2025</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L167" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>276</v>
       </c>
@@ -8033,8 +8543,11 @@
       <c r="K168">
         <v>2025</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L168" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>277</v>
       </c>
@@ -8068,8 +8581,11 @@
       <c r="K169">
         <v>2025</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L169" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>278</v>
       </c>
@@ -8103,8 +8619,11 @@
       <c r="K170">
         <v>2025</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L170" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>279</v>
       </c>
@@ -8138,8 +8657,11 @@
       <c r="K171">
         <v>2025</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L171" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>280</v>
       </c>
@@ -8173,8 +8695,11 @@
       <c r="K172">
         <v>2025</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L172" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>281</v>
       </c>
@@ -8208,8 +8733,11 @@
       <c r="K173">
         <v>2025</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L173" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>282</v>
       </c>
@@ -8243,8 +8771,11 @@
       <c r="K174">
         <v>2025</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L174" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>283</v>
       </c>
@@ -8278,8 +8809,11 @@
       <c r="K175">
         <v>2025</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L175" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>284</v>
       </c>
@@ -8313,8 +8847,11 @@
       <c r="K176">
         <v>2025</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L176" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>285</v>
       </c>
@@ -8348,8 +8885,11 @@
       <c r="K177">
         <v>2025</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L177" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>286</v>
       </c>
@@ -8380,8 +8920,11 @@
       <c r="K178">
         <v>2025</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L178" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>287</v>
       </c>
@@ -8412,8 +8955,11 @@
       <c r="K179">
         <v>2025</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L179" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>288</v>
       </c>
@@ -8447,8 +8993,11 @@
       <c r="K180">
         <v>2025</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L180" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>289</v>
       </c>
@@ -8479,8 +9028,11 @@
       <c r="K181">
         <v>2025</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L181" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>290</v>
       </c>
@@ -8514,8 +9066,11 @@
       <c r="K182">
         <v>2025</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L182" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>291</v>
       </c>
@@ -8549,8 +9104,11 @@
       <c r="K183">
         <v>2025</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L183" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>292</v>
       </c>
@@ -8584,8 +9142,11 @@
       <c r="K184">
         <v>2025</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L184" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>293</v>
       </c>
@@ -8619,8 +9180,11 @@
       <c r="K185">
         <v>2025</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L185" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>294</v>
       </c>
@@ -8654,8 +9218,11 @@
       <c r="K186">
         <v>2025</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L186" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>295</v>
       </c>
@@ -8689,8 +9256,11 @@
       <c r="K187">
         <v>2025</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L187" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>296</v>
       </c>
@@ -8724,8 +9294,11 @@
       <c r="K188">
         <v>2025</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L188" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>297</v>
       </c>
@@ -8759,8 +9332,11 @@
       <c r="K189">
         <v>2025</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L189" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>298</v>
       </c>
@@ -8794,8 +9370,11 @@
       <c r="K190">
         <v>2025</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L190" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>299</v>
       </c>
@@ -8829,8 +9408,11 @@
       <c r="K191">
         <v>2025</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L191" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>300</v>
       </c>
@@ -8864,8 +9446,11 @@
       <c r="K192">
         <v>2025</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L192" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>301</v>
       </c>
@@ -8899,8 +9484,11 @@
       <c r="K193">
         <v>2025</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L193" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>302</v>
       </c>
@@ -8934,8 +9522,11 @@
       <c r="K194">
         <v>2025</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L194" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>303</v>
       </c>
@@ -8969,8 +9560,11 @@
       <c r="K195">
         <v>2025</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L195" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>304</v>
       </c>
@@ -9004,8 +9598,11 @@
       <c r="K196">
         <v>2025</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L196" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>305</v>
       </c>
@@ -9036,8 +9633,11 @@
       <c r="K197">
         <v>2025</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L197" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>306</v>
       </c>
@@ -9071,8 +9671,11 @@
       <c r="K198">
         <v>2025</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L198" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>334</v>
       </c>
@@ -9106,8 +9709,11 @@
       <c r="K199">
         <v>2025</v>
       </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L199" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>335</v>
       </c>
@@ -9138,8 +9744,11 @@
       <c r="K200">
         <v>2025</v>
       </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L200" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>336</v>
       </c>
@@ -9173,8 +9782,11 @@
       <c r="K201">
         <v>2025</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L201" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>337</v>
       </c>
@@ -9208,8 +9820,11 @@
       <c r="K202">
         <v>2025</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L202" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>338</v>
       </c>
@@ -9243,8 +9858,11 @@
       <c r="K203">
         <v>2025</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L203" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>339</v>
       </c>
@@ -9278,8 +9896,11 @@
       <c r="K204">
         <v>2025</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L204" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>340</v>
       </c>
@@ -9313,8 +9934,11 @@
       <c r="K205">
         <v>2025</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L205" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>342</v>
       </c>
@@ -9348,8 +9972,11 @@
       <c r="K206">
         <v>2025</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L206" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>341</v>
       </c>
@@ -9383,8 +10010,11 @@
       <c r="K207">
         <v>2025</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L207" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>343</v>
       </c>
@@ -9418,8 +10048,11 @@
       <c r="K208">
         <v>2025</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L208" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>344</v>
       </c>
@@ -9453,8 +10086,11 @@
       <c r="K209">
         <v>2025</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L209" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>345</v>
       </c>
@@ -9488,8 +10124,11 @@
       <c r="K210">
         <v>2025</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L210" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>346</v>
       </c>
@@ -9523,8 +10162,11 @@
       <c r="K211">
         <v>2025</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L211" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>347</v>
       </c>
@@ -9555,8 +10197,11 @@
       <c r="K212">
         <v>2025</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L212" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>348</v>
       </c>
@@ -9587,8 +10232,11 @@
       <c r="K213">
         <v>2025</v>
       </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L213" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>349</v>
       </c>
@@ -9619,8 +10267,11 @@
       <c r="K214">
         <v>2025</v>
       </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L214" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>350</v>
       </c>
@@ -9654,8 +10305,11 @@
       <c r="K215">
         <v>2025</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L215" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>372</v>
       </c>
@@ -9689,8 +10343,11 @@
       <c r="K216">
         <v>2026</v>
       </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L216" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>373</v>
       </c>
@@ -9721,8 +10378,11 @@
       <c r="K217">
         <v>2026</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L217" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -9756,8 +10416,11 @@
       <c r="K218">
         <v>2026</v>
       </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L218" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>375</v>
       </c>
@@ -9791,8 +10454,11 @@
       <c r="K219">
         <v>2026</v>
       </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L219" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>376</v>
       </c>
@@ -9826,8 +10492,11 @@
       <c r="K220">
         <v>2026</v>
       </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L220" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>377</v>
       </c>
@@ -9861,8 +10530,11 @@
       <c r="K221">
         <v>2026</v>
       </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L221" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>378</v>
       </c>
@@ -9896,8 +10568,11 @@
       <c r="K222">
         <v>2026</v>
       </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L222" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>379</v>
       </c>
@@ -9931,8 +10606,11 @@
       <c r="K223">
         <v>2026</v>
       </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L223" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>380</v>
       </c>
@@ -9966,8 +10644,11 @@
       <c r="K224">
         <v>2026</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L224" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>381</v>
       </c>
@@ -10001,8 +10682,11 @@
       <c r="K225">
         <v>2026</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L225" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>382</v>
       </c>
@@ -10036,8 +10720,11 @@
       <c r="K226">
         <v>2026</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L226" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>383</v>
       </c>
@@ -10071,8 +10758,11 @@
       <c r="K227">
         <v>2026</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L227" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>384</v>
       </c>
@@ -10106,8 +10796,11 @@
       <c r="K228">
         <v>2026</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L228" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>385</v>
       </c>
@@ -10141,8 +10834,11 @@
       <c r="K229">
         <v>2026</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L229" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>386</v>
       </c>
@@ -10176,8 +10872,11 @@
       <c r="K230">
         <v>2026</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L230" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>387</v>
       </c>
@@ -10211,8 +10910,11 @@
       <c r="K231">
         <v>2026</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L231" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>388</v>
       </c>
@@ -10246,8 +10948,11 @@
       <c r="K232">
         <v>2026</v>
       </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L232" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>389</v>
       </c>
@@ -10281,8 +10986,11 @@
       <c r="K233">
         <v>2026</v>
       </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L233" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>390</v>
       </c>
@@ -10313,8 +11021,11 @@
       <c r="K234">
         <v>2026</v>
       </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L234" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>391</v>
       </c>
@@ -10348,8 +11059,11 @@
       <c r="K235">
         <v>2026</v>
       </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L235" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>392</v>
       </c>
@@ -10383,8 +11097,11 @@
       <c r="K236">
         <v>2026</v>
       </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L236" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>393</v>
       </c>
@@ -10418,8 +11135,11 @@
       <c r="K237">
         <v>2026</v>
       </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L237" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>394</v>
       </c>
@@ -10453,8 +11173,11 @@
       <c r="K238">
         <v>2026</v>
       </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L238" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>395</v>
       </c>
@@ -10485,8 +11208,11 @@
       <c r="K239">
         <v>2026</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L239" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>396</v>
       </c>
@@ -10520,8 +11246,11 @@
       <c r="K240">
         <v>2026</v>
       </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L240" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>397</v>
       </c>
@@ -10555,8 +11284,11 @@
       <c r="K241">
         <v>2026</v>
       </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L241" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>406</v>
       </c>
@@ -10590,8 +11322,11 @@
       <c r="K242">
         <v>2026</v>
       </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L242" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>409</v>
       </c>
@@ -10625,8 +11360,11 @@
       <c r="K243">
         <v>2026</v>
       </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L243" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>410</v>
       </c>
@@ -10660,8 +11398,11 @@
       <c r="K244">
         <v>2026</v>
       </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L244" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>411</v>
       </c>
@@ -10695,8 +11436,11 @@
       <c r="K245">
         <v>2026</v>
       </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L245" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>412</v>
       </c>
@@ -10730,8 +11474,11 @@
       <c r="K246">
         <v>2026</v>
       </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L246" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>413</v>
       </c>
@@ -10765,8 +11512,11 @@
       <c r="K247">
         <v>2026</v>
       </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L247" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>414</v>
       </c>
@@ -10800,8 +11550,11 @@
       <c r="K248">
         <v>2026</v>
       </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L248" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>417</v>
       </c>
@@ -10835,8 +11588,11 @@
       <c r="K249">
         <v>2026</v>
       </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L249" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>418</v>
       </c>
@@ -10870,8 +11626,11 @@
       <c r="K250">
         <v>2026</v>
       </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L250" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>419</v>
       </c>
@@ -10905,8 +11664,11 @@
       <c r="K251">
         <v>2026</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L251" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>420</v>
       </c>
@@ -10940,8 +11702,11 @@
       <c r="K252">
         <v>2026</v>
       </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L252" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>421</v>
       </c>
@@ -10975,8 +11740,11 @@
       <c r="K253">
         <v>2026</v>
       </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L253" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>422</v>
       </c>
@@ -11010,8 +11778,11 @@
       <c r="K254">
         <v>2026</v>
       </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L254" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>423</v>
       </c>
@@ -11045,8 +11816,11 @@
       <c r="K255">
         <v>2026</v>
       </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L255" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>426</v>
       </c>
@@ -11080,8 +11854,11 @@
       <c r="K256">
         <v>2026</v>
       </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L256" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>427</v>
       </c>
@@ -11112,8 +11889,11 @@
       <c r="K257">
         <v>2026</v>
       </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L257" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>428</v>
       </c>
@@ -11147,8 +11927,11 @@
       <c r="K258">
         <v>2026</v>
       </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L258" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>429</v>
       </c>
@@ -11182,8 +11965,11 @@
       <c r="K259">
         <v>2026</v>
       </c>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L259" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>430</v>
       </c>
@@ -11217,8 +12003,11 @@
       <c r="K260">
         <v>2026</v>
       </c>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L260" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>431</v>
       </c>
@@ -11251,6 +12040,9 @@
       </c>
       <c r="K261">
         <v>2026</v>
+      </c>
+      <c r="L261" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
